--- a/data/performance/daily/signal_list_2026-06-26.xlsx
+++ b/data/performance/daily/signal_list_2026-06-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-26.xlsx
+++ b/data/performance/daily/signal_list_2026-06-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -602,15 +613,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -686,15 +707,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -728,15 +754,20 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -770,15 +801,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -896,15 +942,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1022,15 +1083,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1064,15 +1130,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1106,15 +1177,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1148,15 +1224,20 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1188,17 +1269,22 @@
       <c r="G20" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-1.77</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1257,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1267,9 +1358,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1299,7 +1391,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1324,15 +1416,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G5" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1406,17 +1508,22 @@
       <c r="G6" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1448,17 +1555,22 @@
       <c r="G7" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1492,15 +1604,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1534,15 +1651,20 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1576,15 +1698,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1618,15 +1745,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1660,15 +1792,20 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1702,15 +1839,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1742,17 +1884,22 @@
       <c r="G14" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1786,15 +1933,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1828,15 +1980,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1868,17 +2025,22 @@
       <c r="G17" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1912,15 +2074,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1954,15 +2121,20 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1996,15 +2168,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2038,15 +2215,20 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2080,15 +2262,20 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2120,17 +2307,22 @@
       <c r="G23" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2164,15 +2356,20 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2206,15 +2403,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G26" s="4" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2332,15 +2544,20 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2374,15 +2591,20 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2416,15 +2638,20 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2458,15 +2685,20 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2500,15 +2732,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2542,15 +2779,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2584,15 +2826,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2624,17 +2871,22 @@
       <c r="G35" s="4" t="n">
         <v>20.23</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G36" s="4" t="n">
         <v>7.35</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2710,15 +2967,20 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G38" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2792,17 +3059,22 @@
       <c r="G39" s="4" t="n">
         <v>-14.64</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2834,17 +3106,22 @@
       <c r="G40" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2878,15 +3155,20 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2920,15 +3202,20 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2960,17 +3247,22 @@
       <c r="G43" s="4" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3002,17 +3294,22 @@
       <c r="G44" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,17 +3341,22 @@
       <c r="G45" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3086,17 +3388,22 @@
       <c r="G46" s="4" t="n">
         <v>-6.72</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3128,17 +3435,22 @@
       <c r="G47" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G48" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3214,15 +3531,20 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3256,15 +3578,20 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3298,15 +3625,20 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3338,17 +3670,22 @@
       <c r="G52" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-26.xlsx
+++ b/data/performance/daily/signal_list_2026-06-26.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>378</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>378</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>380</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.53</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>1549.49</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>1465</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1555</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.36</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-5.45</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>141</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>136</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>142</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>16900</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>16550</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>17100</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-2.07</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>1130</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>1100</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1145</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>99</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>94</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>105</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-5.05</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>1520</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>1515</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1520</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-0.33</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>980</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>970</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>980</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.02</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>2500</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>2500</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>2580</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>940</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>950</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>955</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>1.06</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>7850</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>7575</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>8200</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>286</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>280</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>290</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>615</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>585</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>700</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>13.82</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-4.88</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>384</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>370</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>390</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-3.65</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>645</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>630</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>650</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-2.33</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>202</v>
       </c>
       <c r="D20" t="n">
-        <v>212</v>
+        <v/>
       </c>
       <c r="E20" t="n">
         <v>212</v>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>4.95</v>
+      <c r="F20" t="n">
+        <v>212</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H20" s="4" t="n">
+        <v>4.95</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>555</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>565</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-1.77</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1348,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1356,12 +1413,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1391,45 +1449,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>910</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>955</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>995</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>9.34</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>760</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>765</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>780</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>2.63</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>1690</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>1685</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1690</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>11800</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>11750</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>12300</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>4.24</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.42</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1638,33 +1713,36 @@
         <v>378</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>378</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>380</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.53</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1685,33 +1763,36 @@
         <v>1549.49</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>1465</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1555</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0.36</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-5.45</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1732,33 +1813,36 @@
         <v>141</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>136</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>142</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1779,33 +1863,36 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>69</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>80</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>14.29</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1826,33 +1913,36 @@
         <v>16900</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>16550</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>17100</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-2.07</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1873,33 +1963,36 @@
         <v>108</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>117</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>119</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>10.19</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1920,33 +2013,36 @@
         <v>3160</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>2940</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>3170</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-6.96</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1967,33 +2063,36 @@
         <v>99</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>94</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>105</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>6.06</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-5.05</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2014,33 +2113,36 @@
         <v>780</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>790</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>795</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2061,33 +2163,36 @@
         <v>3010</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>2700</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>3050</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-10.3</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2108,33 +2213,36 @@
         <v>1735</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>1700</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1750</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.86</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-2.02</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2155,33 +2263,36 @@
         <v>1895</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>1870</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1900</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-1.32</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2202,33 +2313,36 @@
         <v>1860</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>1840</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1865</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-1.08</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2249,33 +2363,36 @@
         <v>2880</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>2810</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2950</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>2.43</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-2.43</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2296,33 +2413,36 @@
         <v>372</v>
       </c>
       <c r="D23" t="n">
-        <v>400</v>
+        <v/>
       </c>
       <c r="E23" t="n">
         <v>400</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>7.53</v>
+      <c r="F23" t="n">
+        <v>400</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>7.53</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H23" s="4" t="n">
+        <v>7.53</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2343,33 +2463,36 @@
         <v>70</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>69</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>71</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-1.43</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2390,33 +2513,36 @@
         <v>720</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>700</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>845</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>17.36</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2437,33 +2563,36 @@
         <v>530</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>525</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>530</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2484,33 +2613,36 @@
         <v>1845</v>
       </c>
       <c r="D27" t="n">
-        <v>1845</v>
+        <v/>
       </c>
       <c r="E27" t="n">
         <v>1845</v>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>0</v>
+      <c r="F27" t="n">
+        <v>1845</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2531,33 +2663,36 @@
         <v>1515</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>1505</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>1625</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>7.26</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-0.66</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2578,33 +2713,36 @@
         <v>7850</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>7575</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>8200</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2625,33 +2763,36 @@
         <v>332</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>330</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>336</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2672,33 +2813,36 @@
         <v>635</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>630</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>650</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>2.36</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2719,33 +2863,36 @@
         <v>169</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>166</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>188</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>11.24</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-1.78</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2766,33 +2913,36 @@
         <v>286</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>280</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>290</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2813,33 +2963,36 @@
         <v>137</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>128</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>139</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-6.57</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2860,33 +3013,36 @@
         <v>1730</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>2080</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>2160</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>24.86</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>20.23</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2907,33 +3063,36 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>73</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>76</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>7.35</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2954,33 +3113,36 @@
         <v>286</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>270</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>292</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-5.59</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3001,33 +3163,36 @@
         <v>640</v>
       </c>
       <c r="D38" t="n">
-        <v>645</v>
+        <v/>
       </c>
       <c r="E38" t="n">
         <v>645</v>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>0.78</v>
+      <c r="F38" t="n">
+        <v>645</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H38" s="4" t="n">
+        <v>0.78</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>478</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>408</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>478</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>-14.64</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>486</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>488</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>490</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>384</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>370</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>390</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-3.65</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>645</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>630</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>650</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-2.33</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>218</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>206</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>218</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>176</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>179</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>183</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>3.98</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>141</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>136</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>141</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>595</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>555</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>590</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>-0.84</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>-6.72</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>288</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>280</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>284</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>202</v>
       </c>
       <c r="D48" t="n">
-        <v>212</v>
+        <v/>
       </c>
       <c r="E48" t="n">
         <v>212</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>4.95</v>
+      <c r="F48" t="n">
+        <v>212</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H48" s="4" t="n">
+        <v>4.95</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>1250</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>1250</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>1275</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>93</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>86</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>94</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-7.53</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>1635</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>1395</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>2040</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>24.77</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>-14.68</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>99</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>100</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>104</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>5.05</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-26.xlsx
+++ b/data/performance/daily/signal_list_2026-06-26.xlsx
@@ -559,7 +559,7 @@
         <v>378</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>329.74</v>
       </c>
       <c r="E5" t="n">
         <v>378</v>
@@ -609,7 +609,7 @@
         <v>1549.49</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1550</v>
       </c>
       <c r="E6" t="n">
         <v>1465</v>
@@ -659,7 +659,7 @@
         <v>141</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>141</v>
       </c>
       <c r="E7" t="n">
         <v>136</v>
@@ -709,7 +709,7 @@
         <v>16900</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>16055</v>
       </c>
       <c r="E8" t="n">
         <v>16550</v>
@@ -759,7 +759,7 @@
         <v>1130</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E9" t="n">
         <v>1100</v>
@@ -809,7 +809,7 @@
         <v>99</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
         <v>94</v>
@@ -859,7 +859,7 @@
         <v>1520</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>1510</v>
       </c>
       <c r="E11" t="n">
         <v>1515</v>
@@ -909,7 +909,7 @@
         <v>980</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>980</v>
       </c>
       <c r="E12" t="n">
         <v>970</v>
@@ -959,7 +959,7 @@
         <v>2500</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>2530</v>
       </c>
       <c r="E13" t="n">
         <v>2500</v>
@@ -1009,7 +1009,7 @@
         <v>940</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>923.0599999999999</v>
       </c>
       <c r="E14" t="n">
         <v>950</v>
@@ -1059,7 +1059,7 @@
         <v>7850</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>7875</v>
       </c>
       <c r="E15" t="n">
         <v>7575</v>
@@ -1109,7 +1109,7 @@
         <v>286</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="E16" t="n">
         <v>280</v>
@@ -1159,7 +1159,7 @@
         <v>615</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>675</v>
       </c>
       <c r="E17" t="n">
         <v>585</v>
@@ -1209,7 +1209,7 @@
         <v>384</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>384</v>
       </c>
       <c r="E18" t="n">
         <v>370</v>
@@ -1259,7 +1259,7 @@
         <v>645</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E19" t="n">
         <v>630</v>
@@ -1309,7 +1309,7 @@
         <v>202</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>199</v>
       </c>
       <c r="E20" t="n">
         <v>212</v>
@@ -1359,7 +1359,7 @@
         <v>565</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>565</v>
       </c>
       <c r="E21" t="n">
         <v>555</v>
@@ -1513,7 +1513,7 @@
         <v>910</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>910</v>
       </c>
       <c r="E5" t="n">
         <v>955</v>
@@ -1563,7 +1563,7 @@
         <v>760</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>755</v>
       </c>
       <c r="E6" t="n">
         <v>765</v>
@@ -1613,7 +1613,7 @@
         <v>1690</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1523.51</v>
       </c>
       <c r="E7" t="n">
         <v>1685</v>
@@ -1663,7 +1663,7 @@
         <v>11800</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>11800</v>
       </c>
       <c r="E8" t="n">
         <v>11750</v>
@@ -1713,7 +1713,7 @@
         <v>378</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>329.74</v>
       </c>
       <c r="E9" t="n">
         <v>378</v>
@@ -1763,7 +1763,7 @@
         <v>1549.49</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>1550</v>
       </c>
       <c r="E10" t="n">
         <v>1465</v>
@@ -1813,7 +1813,7 @@
         <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>141</v>
       </c>
       <c r="E11" t="n">
         <v>136</v>
@@ -1863,7 +1863,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
         <v>69</v>
@@ -1913,7 +1913,7 @@
         <v>16900</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>16055</v>
       </c>
       <c r="E13" t="n">
         <v>16550</v>
@@ -1963,7 +1963,7 @@
         <v>108</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>109</v>
       </c>
       <c r="E14" t="n">
         <v>117</v>
@@ -2013,7 +2013,7 @@
         <v>3160</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>3160</v>
       </c>
       <c r="E15" t="n">
         <v>2940</v>
@@ -2063,7 +2063,7 @@
         <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E16" t="n">
         <v>94</v>
@@ -2113,7 +2113,7 @@
         <v>780</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>790</v>
       </c>
       <c r="E17" t="n">
         <v>790</v>
@@ -2163,7 +2163,7 @@
         <v>3010</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>3020</v>
       </c>
       <c r="E18" t="n">
         <v>2700</v>
@@ -2213,7 +2213,7 @@
         <v>1735</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>1715</v>
       </c>
       <c r="E19" t="n">
         <v>1700</v>
@@ -2263,7 +2263,7 @@
         <v>1895</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>1895</v>
       </c>
       <c r="E20" t="n">
         <v>1870</v>
@@ -2313,7 +2313,7 @@
         <v>1860</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1610</v>
       </c>
       <c r="E21" t="n">
         <v>1840</v>
@@ -2363,7 +2363,7 @@
         <v>2880</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>2890</v>
       </c>
       <c r="E22" t="n">
         <v>2810</v>
@@ -2413,7 +2413,7 @@
         <v>372</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>376</v>
       </c>
       <c r="E23" t="n">
         <v>400</v>
@@ -2463,7 +2463,7 @@
         <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
         <v>69</v>
@@ -2513,7 +2513,7 @@
         <v>720</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>720</v>
       </c>
       <c r="E25" t="n">
         <v>700</v>
@@ -2563,7 +2563,7 @@
         <v>530</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>530</v>
       </c>
       <c r="E26" t="n">
         <v>525</v>
@@ -2613,7 +2613,7 @@
         <v>1845</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>1845</v>
       </c>
       <c r="E27" t="n">
         <v>1845</v>
@@ -2663,7 +2663,7 @@
         <v>1515</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>1515</v>
       </c>
       <c r="E28" t="n">
         <v>1505</v>
@@ -2713,7 +2713,7 @@
         <v>7850</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>7875</v>
       </c>
       <c r="E29" t="n">
         <v>7575</v>
@@ -2763,7 +2763,7 @@
         <v>332</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>312.17</v>
       </c>
       <c r="E30" t="n">
         <v>330</v>
@@ -2813,7 +2813,7 @@
         <v>635</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>635.84</v>
       </c>
       <c r="E31" t="n">
         <v>630</v>
@@ -2863,7 +2863,7 @@
         <v>169</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>169</v>
       </c>
       <c r="E32" t="n">
         <v>166</v>
@@ -2913,7 +2913,7 @@
         <v>286</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="E33" t="n">
         <v>280</v>
@@ -2963,7 +2963,7 @@
         <v>137</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>136.46</v>
       </c>
       <c r="E34" t="n">
         <v>128</v>
@@ -3013,7 +3013,7 @@
         <v>1730</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1685</v>
       </c>
       <c r="E35" t="n">
         <v>2080</v>
@@ -3063,7 +3063,7 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>68</v>
       </c>
       <c r="E36" t="n">
         <v>73</v>
@@ -3113,7 +3113,7 @@
         <v>286</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>288</v>
       </c>
       <c r="E37" t="n">
         <v>270</v>
@@ -3163,7 +3163,7 @@
         <v>640</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E38" t="n">
         <v>645</v>
@@ -3213,7 +3213,7 @@
         <v>478</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>478</v>
       </c>
       <c r="E39" t="n">
         <v>408</v>
@@ -3263,7 +3263,7 @@
         <v>486</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>486</v>
       </c>
       <c r="E40" t="n">
         <v>488</v>
@@ -3313,7 +3313,7 @@
         <v>384</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>384</v>
       </c>
       <c r="E41" t="n">
         <v>370</v>
@@ -3363,7 +3363,7 @@
         <v>645</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E42" t="n">
         <v>630</v>
@@ -3413,7 +3413,7 @@
         <v>218</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>218</v>
       </c>
       <c r="E43" t="n">
         <v>206</v>
@@ -3463,7 +3463,7 @@
         <v>176</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>176</v>
       </c>
       <c r="E44" t="n">
         <v>179</v>
@@ -3513,7 +3513,7 @@
         <v>141</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>141</v>
       </c>
       <c r="E45" t="n">
         <v>136</v>
@@ -3563,7 +3563,7 @@
         <v>595</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>590</v>
       </c>
       <c r="E46" t="n">
         <v>555</v>
@@ -3613,7 +3613,7 @@
         <v>288</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>284</v>
       </c>
       <c r="E47" t="n">
         <v>280</v>
@@ -3663,7 +3663,7 @@
         <v>202</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>199</v>
       </c>
       <c r="E48" t="n">
         <v>212</v>
@@ -3713,7 +3713,7 @@
         <v>1250</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>1244.66</v>
       </c>
       <c r="E49" t="n">
         <v>1250</v>
@@ -3763,7 +3763,7 @@
         <v>93</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>93</v>
       </c>
       <c r="E50" t="n">
         <v>86</v>
@@ -3813,7 +3813,7 @@
         <v>1635</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>1810</v>
       </c>
       <c r="E51" t="n">
         <v>1395</v>
@@ -3863,7 +3863,7 @@
         <v>99</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>98</v>
       </c>
       <c r="E52" t="n">
         <v>100</v>
